--- a/Design/Datas/演出/演出表.xlsx
+++ b/Design/Datas/演出/演出表.xlsx
@@ -1068,7 +1068,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="14.125" customWidth="1"/>
@@ -1078,7 +1078,7 @@
     <col min="6" max="6" width="34.9166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:5">
+    <row r="1" s="1" customFormat="1" spans="1:6">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1092,8 +1092,13 @@
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>onCompletedActionId</t>
+        </is>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:5">
+    <row r="2" s="2" customFormat="1" spans="1:6">
       <c r="A2" s="5" t="s">
         <v>4</v>
       </c>
@@ -1107,13 +1112,19 @@
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>int?#ref=ActionTable</t>
+        </is>
+      </c>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:5">
+    <row r="3" s="2" customFormat="1" spans="1:6">
       <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
+      <c r="F3" s="2"/>
     </row>
-    <row r="4" s="3" customFormat="1" spans="1:5">
+    <row r="4" s="3" customFormat="1" spans="1:6">
       <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
@@ -1129,8 +1140,13 @@
       <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>正常结束行为</t>
+        </is>
+      </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:6">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
         <v>1</v>
@@ -1144,13 +1160,15 @@
       <c r="E5" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="F5" s="2"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:6">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
